--- a/data/trans_camb/IP18A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-33,53</t>
+          <t>18,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,74</t>
+          <t>22,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-24,13</t>
+          <t>20,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 14,66</t>
+          <t>-5,21; 13,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 15,43</t>
+          <t>-4,23; 15,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,48; -12,26</t>
+          <t>-2,36; 31,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 7,41</t>
+          <t>-10,54; 8,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 12,28</t>
+          <t>-7,78; 11,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 4,26</t>
+          <t>6,66; 34,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 8,19</t>
+          <t>-5,41; 9,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 10,82</t>
+          <t>-2,6; 12,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -10,11</t>
+          <t>7,33; 29,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-53,56%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,65%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,47%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 25,9</t>
+          <t>-8,07; 24,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 26,56</t>
+          <t>-6,0; 27,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,45; -18,52</t>
+          <t>-2,92; 53,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 13,07</t>
+          <t>-15,85; 15,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 21,22</t>
+          <t>-11,41; 20,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 7,32</t>
+          <t>9,8; 60,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 13,93</t>
+          <t>-8,26; 15,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 18,23</t>
+          <t>-3,91; 20,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; -16,52</t>
+          <t>11,6; 50,65</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-43,18</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-44,44</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-44,29</t>
+          <t>8,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,08</t>
+          <t>-6,14; 9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 6,79</t>
+          <t>-7,77; 7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -27,26</t>
+          <t>-5,27; 22,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 14,77</t>
+          <t>-0,24; 14,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 11,79</t>
+          <t>-3,73; 11,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,87; -31,26</t>
+          <t>-5,29; 19,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,03</t>
+          <t>-0,51; 10,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 7,11</t>
+          <t>-4,29; 7,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-52,81; -34,43</t>
+          <t>-0,46; 16,96</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-63,84%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-68,55%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-66,93%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 13,97</t>
+          <t>-8,81; 13,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 10,84</t>
+          <t>-10,92; 11,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,25; -41,22</t>
+          <t>-7,61; 34,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 24,44</t>
+          <t>-0,48; 23,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 19,34</t>
+          <t>-5,4; 19,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -49,47</t>
+          <t>-7,88; 31,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 15,8</t>
+          <t>-0,78; 16,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 11,43</t>
+          <t>-6,22; 11,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,27; -51,63</t>
+          <t>-0,67; 26,43</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,38</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-18,61</t>
+          <t>22,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,41</t>
+          <t>17,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 10,49</t>
+          <t>-6,62; 11,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 10,13</t>
+          <t>-7,04; 9,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 12,08</t>
+          <t>-6,41; 26,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 12,45</t>
+          <t>-5,94; 11,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 5,96</t>
+          <t>-12,52; 5,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 1,04</t>
+          <t>8,12; 32,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 9,38</t>
+          <t>-3,23; 8,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 6,11</t>
+          <t>-7,4; 5,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 1,51</t>
+          <t>5,41; 25,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,69%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-28,86%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-22,45%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 17,93</t>
+          <t>-9,8; 19,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 17,19</t>
+          <t>-10,34; 16,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 18,59</t>
+          <t>-8,59; 43,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 21,03</t>
+          <t>-8,92; 18,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 10,05</t>
+          <t>-17,55; 10,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 1,85</t>
+          <t>11,99; 53,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 15,67</t>
+          <t>-4,88; 14,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 10,1</t>
+          <t>-10,97; 8,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 1,85</t>
+          <t>8,14; 41,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-19,53</t>
+          <t>18,36</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-38,63</t>
+          <t>13,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-29,03</t>
+          <t>16,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 10,07</t>
+          <t>-7,6; 10,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 11,1</t>
+          <t>-5,75; 10,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-35,22; -2,39</t>
+          <t>3,21; 31,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 3,76</t>
+          <t>-12,68; 4,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 6,72</t>
+          <t>-10,45; 5,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-51,71; -20,3</t>
+          <t>-1,1; 26,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 4,69</t>
+          <t>-7,07; 4,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 6,42</t>
+          <t>-5,25; 6,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-39,91; -16,95</t>
+          <t>4,95; 25,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-33,61%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-59,52%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-47,27%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 18,41</t>
+          <t>-11,98; 19,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 20,11</t>
+          <t>-9,2; 19,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,03; -3,51</t>
+          <t>6,56; 58,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 6,62</t>
+          <t>-18,25; 6,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 11,03</t>
+          <t>-15,02; 9,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,35; -31,45</t>
+          <t>-1,27; 42,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 8,04</t>
+          <t>-11,0; 8,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 11,19</t>
+          <t>-8,32; 10,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,1; -28,22</t>
+          <t>8,31; 43,29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-25,77</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-32,33</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-29,4</t>
+          <t>14,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,68</t>
+          <t>-2,05; 6,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 6,82</t>
+          <t>-2,34; 6,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,73</t>
+          <t>6,32; 21,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,79</t>
+          <t>-2,49; 5,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,65</t>
+          <t>-3,93; 4,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,51; -24,62</t>
+          <t>8,26; 20,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,86</t>
+          <t>-1,24; 4,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,55</t>
+          <t>-1,67; 4,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -22,61</t>
+          <t>9,67; 19,68</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-41,03%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,24%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-46,23%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 10,87</t>
+          <t>-3,25; 11,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,3</t>
+          <t>-3,4; 11,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,83; -27,21</t>
+          <t>9,46; 34,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,29</t>
+          <t>-3,8; 9,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 7,54</t>
+          <t>-5,82; 7,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -38,42</t>
+          <t>12,52; 33,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,83</t>
+          <t>-1,69; 8,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,31</t>
+          <t>-2,53; 7,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -36,14</t>
+          <t>15,1; 31,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 13,84</t>
+          <t>-5,71; 14,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 15,92</t>
+          <t>-4,16; 15,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 31,54</t>
+          <t>-2,09; 31,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 8,86</t>
+          <t>-10,12; 8,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 11,69</t>
+          <t>-6,97; 12,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 34,83</t>
+          <t>6,5; 34,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 9,08</t>
+          <t>-4,9; 8,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 12,0</t>
+          <t>-3,35; 10,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 29,8</t>
+          <t>8,06; 30,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 24,29</t>
+          <t>-8,25; 24,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 27,57</t>
+          <t>-6,26; 27,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 53,92</t>
+          <t>-1,28; 54,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 15,66</t>
+          <t>-14,85; 14,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 20,41</t>
+          <t>-10,51; 21,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 60,26</t>
+          <t>10,72; 59,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 15,86</t>
+          <t>-7,52; 15,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 20,51</t>
+          <t>-5,05; 17,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 50,65</t>
+          <t>13,09; 50,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 9,02</t>
+          <t>-6,58; 8,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 7,32</t>
+          <t>-8,35; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 22,85</t>
+          <t>-5,41; 22,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 14,59</t>
+          <t>-0,52; 14,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 11,57</t>
+          <t>-4,86; 11,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 19,59</t>
+          <t>-6,15; 18,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 10,42</t>
+          <t>-0,97; 9,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 7,11</t>
+          <t>-3,34; 7,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 16,96</t>
+          <t>-0,49; 16,48</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 13,77</t>
+          <t>-9,19; 13,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 11,39</t>
+          <t>-11,69; 11,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 34,86</t>
+          <t>-7,28; 34,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 23,75</t>
+          <t>-0,99; 23,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 19,41</t>
+          <t>-7,13; 18,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 31,54</t>
+          <t>-8,75; 29,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 16,52</t>
+          <t>-1,34; 15,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 11,14</t>
+          <t>-4,89; 12,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 26,43</t>
+          <t>-0,59; 25,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 11,35</t>
+          <t>-7,39; 11,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 9,93</t>
+          <t>-8,81; 9,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 26,02</t>
+          <t>-7,86; 25,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 11,04</t>
+          <t>-5,4; 12,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 5,82</t>
+          <t>-11,96; 6,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 32,34</t>
+          <t>7,27; 32,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 8,99</t>
+          <t>-3,26; 9,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 5,07</t>
+          <t>-6,93; 6,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 25,5</t>
+          <t>5,2; 26,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 19,41</t>
+          <t>-10,67; 19,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 16,54</t>
+          <t>-13,23; 16,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 43,3</t>
+          <t>-11,86; 42,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 18,68</t>
+          <t>-7,86; 20,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 10,05</t>
+          <t>-17,47; 10,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,99; 53,54</t>
+          <t>12,2; 54,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 14,63</t>
+          <t>-4,94; 15,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 8,16</t>
+          <t>-10,36; 9,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 41,51</t>
+          <t>7,8; 42,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 10,39</t>
+          <t>-6,96; 10,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 10,5</t>
+          <t>-5,77; 11,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 31,88</t>
+          <t>3,15; 31,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 4,02</t>
+          <t>-12,0; 4,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 5,72</t>
+          <t>-9,99; 6,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 26,18</t>
+          <t>-1,96; 26,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 4,81</t>
+          <t>-6,88; 4,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 6,3</t>
+          <t>-5,02; 6,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 25,12</t>
+          <t>4,7; 24,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 19,68</t>
+          <t>-11,34; 20,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 19,39</t>
+          <t>-9,41; 21,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 58,35</t>
+          <t>6,54; 57,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 6,61</t>
+          <t>-17,55; 7,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 9,49</t>
+          <t>-14,63; 10,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 42,92</t>
+          <t>-2,31; 42,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 8,2</t>
+          <t>-10,87; 8,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 10,77</t>
+          <t>-7,91; 12,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 43,29</t>
+          <t>7,81; 41,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,82</t>
+          <t>-2,13; 6,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,79</t>
+          <t>-1,84; 6,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,55</t>
+          <t>5,84; 21,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,83</t>
+          <t>-2,84; 5,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,69</t>
+          <t>-3,48; 4,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,26; 20,89</t>
+          <t>8,61; 21,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,89</t>
+          <t>-1,12; 4,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,41</t>
+          <t>-1,65; 4,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,68</t>
+          <t>9,58; 20,05</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 11,21</t>
+          <t>-3,29; 11,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,38</t>
+          <t>-2,84; 11,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,97</t>
+          <t>9,32; 35,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 9,42</t>
+          <t>-4,27; 9,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 7,59</t>
+          <t>-5,33; 7,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,52; 33,61</t>
+          <t>13,08; 34,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,11</t>
+          <t>-1,7; 7,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,15</t>
+          <t>-2,56; 6,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,1; 31,39</t>
+          <t>14,58; 31,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22,8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,72</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,14</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,81</t>
+          <t>19,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>21,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 14,52</t>
+          <t>-11,28; 7,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 15,83</t>
+          <t>-7,02; 12,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 31,7</t>
+          <t>5,82; 34,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 8,32</t>
+          <t>-5,59; 14,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 12,71</t>
+          <t>-4,29; 15,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 34,31</t>
+          <t>-1,21; 32,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 8,88</t>
+          <t>-5,63; 8,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 10,37</t>
+          <t>-3,0; 10,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 30,17</t>
+          <t>8,62; 30,54</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-1,32%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>9,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28,98%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,32%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 24,67</t>
+          <t>-16,15; 13,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 27,93</t>
+          <t>-10,71; 21,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 54,32</t>
+          <t>9,65; 59,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 14,35</t>
+          <t>-8,07; 25,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 21,62</t>
+          <t>-6,55; 26,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 59,1</t>
+          <t>-1,52; 55,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 15,13</t>
+          <t>-8,69; 13,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 17,56</t>
+          <t>-4,46; 18,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,09; 50,87</t>
+          <t>13,35; 50,8</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,14</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 8,84</t>
+          <t>-0,7; 14,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 7,4</t>
+          <t>-4,23; 11,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 22,08</t>
+          <t>-6,3; 19,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,31</t>
+          <t>-6,27; 9,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 11,05</t>
+          <t>-8,18; 6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 18,21</t>
+          <t>-11,71; 20,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 9,8</t>
+          <t>-0,77; 10,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 7,53</t>
+          <t>-4,32; 7,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 16,48</t>
+          <t>-2,55; 15,97</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-0,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 13,68</t>
+          <t>-1,06; 24,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 11,6</t>
+          <t>-6,13; 19,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 34,11</t>
+          <t>-9,64; 31,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 23,54</t>
+          <t>-8,81; 13,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 18,08</t>
+          <t>-11,64; 10,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 29,09</t>
+          <t>-16,15; 31,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 15,65</t>
+          <t>-1,08; 15,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 12,02</t>
+          <t>-6,23; 11,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 25,58</t>
+          <t>-3,81; 24,8</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22,4</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,36</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,8</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,18</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,24</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,08</t>
+          <t>15,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 11,45</t>
+          <t>-5,46; 12,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 9,58</t>
+          <t>-12,71; 5,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 25,19</t>
+          <t>7,35; 33,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,32</t>
+          <t>-7,47; 10,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 6,29</t>
+          <t>-7,82; 10,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 32,13</t>
+          <t>-10,58; 22,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,2</t>
+          <t>-3,91; 9,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 6,0</t>
+          <t>-7,55; 6,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 26,08</t>
+          <t>2,9; 25,39</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-4,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-4,93%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 19,89</t>
+          <t>-7,88; 21,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 16,63</t>
+          <t>-18,53; 10,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 42,14</t>
+          <t>12,44; 56,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 20,99</t>
+          <t>-10,67; 17,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 10,42</t>
+          <t>-11,43; 17,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,2; 54,63</t>
+          <t>-15,75; 37,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 15,27</t>
+          <t>-5,83; 15,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 9,69</t>
+          <t>-11,3; 10,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 42,02</t>
+          <t>4,78; 41,04</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13,2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,76</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,05</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,74</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>17,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,12</t>
+          <t>15,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 10,21</t>
+          <t>-12,17; 3,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 11,47</t>
+          <t>-9,71; 6,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 31,24</t>
+          <t>-3,02; 25,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 4,26</t>
+          <t>-7,28; 10,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 6,39</t>
+          <t>-5,53; 11,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 26,35</t>
+          <t>1,4; 31,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 4,94</t>
+          <t>-6,98; 4,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 6,98</t>
+          <t>-5,16; 6,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 24,58</t>
+          <t>4,67; 25,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-6,24%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-2,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20,34%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>31,59%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-6,24%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-2,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 20,01</t>
+          <t>-17,55; 6,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 21,65</t>
+          <t>-14,28; 11,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 57,76</t>
+          <t>-4,17; 42,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 7,11</t>
+          <t>-11,39; 18,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 10,46</t>
+          <t>-9,0; 20,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 42,8</t>
+          <t>2,7; 57,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 8,54</t>
+          <t>-10,81; 8,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 12,03</t>
+          <t>-8,09; 11,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,81; 41,98</t>
+          <t>7,54; 41,98</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,26</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,94</t>
+          <t>-2,68; 5,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,97</t>
+          <t>-4,07; 4,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 21,44</t>
+          <t>7,8; 21,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,89</t>
+          <t>-2,24; 6,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,77</t>
+          <t>-2,03; 6,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,61; 21,31</t>
+          <t>3,9; 20,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,85</t>
+          <t>-1,24; 4,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,18</t>
+          <t>-1,62; 4,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,58; 20,05</t>
+          <t>8,23; 18,7</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,35</t>
+          <t>-4,09; 9,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,62</t>
+          <t>-6,16; 7,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,32; 35,39</t>
+          <t>11,66; 33,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 9,44</t>
+          <t>-3,44; 10,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 7,64</t>
+          <t>-3,09; 11,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,08; 34,03</t>
+          <t>6,21; 33,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,83</t>
+          <t>-1,9; 7,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,7</t>
+          <t>-2,5; 7,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,58; 31,81</t>
+          <t>12,82; 29,97</t>
         </is>
       </c>
     </row>
